--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513304_ELIMINGRE12FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513304_ELIMINGRE12FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7009</v>
+        <v>4.059</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1366</v>
+        <v>-0.1257</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8375</v>
+        <v>4.1847</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2557</v>
+        <v>-0.2424</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1909</v>
+        <v>1.21</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.4467</v>
+        <v>-1.4524</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.0231</v>
+        <v>-1.7953</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2069</v>
+        <v>1.3651</v>
       </c>
       <c r="L2" t="n">
-        <v>-3.23</v>
+        <v>-3.1604</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7674</v>
+        <v>1.5529</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0159</v>
+        <v>-0.1551</v>
       </c>
       <c r="O2" t="n">
-        <v>1.7834</v>
+        <v>1.708</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.8008</v>
+        <v>-2.7263</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8186</v>
+        <v>-0.0192</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6293</v>
+        <v>0.1532</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1893</v>
+        <v>-0.1724</v>
       </c>
       <c r="V2" t="n">
-        <v>6.9388</v>
+        <v>7.0469</v>
       </c>
       <c r="W2" t="n">
-        <v>6.2587</v>
+        <v>6.3848</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5202</v>
+        <v>2.7427</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1525</v>
+        <v>2.1176</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3677</v>
+        <v>0.6251</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6826</v>
+        <v>2.6682</v>
       </c>
       <c r="H3" t="n">
-        <v>0.911</v>
+        <v>0.9226</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7716</v>
+        <v>1.7456</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2413</v>
+        <v>2.3234</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5614</v>
+        <v>1.6344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6889</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4413</v>
+        <v>0.3448</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6503</v>
+        <v>-0.7118</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0917</v>
+        <v>1.0566</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7028</v>
+        <v>-0.425</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0888</v>
+        <v>-0.2058</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.614</v>
+        <v>-0.2192</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7864</v>
+        <v>1.835</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4443</v>
+        <v>0.0338</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2307</v>
+        <v>1.8012</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2592</v>
+        <v>0.3239</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6952</v>
+        <v>1.734</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.436</v>
+        <v>-1.4101</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2233</v>
+        <v>-0.9816</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1248</v>
+        <v>2.276</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.3481</v>
+        <v>-3.2576</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4825</v>
+        <v>1.3055</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4297</v>
+        <v>-0.542</v>
       </c>
       <c r="O4" t="n">
-        <v>1.9121</v>
+        <v>1.8475</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4725</v>
+        <v>-0.5152</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.54</v>
+        <v>-0.4015</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0675</v>
+        <v>-0.1138</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3192</v>
+        <v>2.3905</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -799,31 +799,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4997</v>
+        <v>1.5237</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4997</v>
+        <v>1.5237</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4997</v>
+        <v>1.5237</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4997</v>
+        <v>1.5237</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. LOPEZ ABAD</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3791</v>
+        <v>1.4521</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1359</v>
+        <v>0.1884</v>
       </c>
       <c r="F6" t="n">
-        <v>1.515</v>
+        <v>1.2637</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9941</v>
+        <v>0.897</v>
       </c>
       <c r="H6" t="n">
-        <v>1.436</v>
+        <v>0.3469</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4418</v>
+        <v>0.5501</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7598</v>
+        <v>1.4285</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6798</v>
+        <v>0.9981</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08</v>
+        <v>0.4303</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2343</v>
+        <v>-0.5315</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7562</v>
+        <v>-0.6513</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5218</v>
+        <v>0.1198</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8002</v>
+        <v>1.3632</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8005</v>
+        <v>2.3368</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.916</v>
+        <v>-0.5286</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1046</v>
+        <v>0.0646</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0206</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5007</v>
+        <v>-0.2795</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5007</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. RUIPEREZ SANCHEZ</t>
+          <t>G. LOPEZ ABAD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7473</v>
+        <v>1.3619</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.85</v>
+        <v>-0.1772</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5973</v>
+        <v>1.5391</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5425</v>
+        <v>0.9409</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8761</v>
+        <v>1.4111</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3337</v>
+        <v>-0.4702</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6342</v>
+        <v>0.7789</v>
       </c>
       <c r="K7" t="n">
-        <v>0.12</v>
+        <v>0.6979</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7542</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1767</v>
+        <v>0.1619</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7562</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4205</v>
+        <v>-0.5513</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6005</v>
+        <v>1.7526</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0643</v>
+        <v>-0.7921</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.0175</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5395</v>
+        <v>-0.8096</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4596</v>
+        <v>0.4342</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7194</v>
+        <v>0.4342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>J. CARRERAS MUÑOZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3755</v>
+        <v>0.3079</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9387</v>
+        <v>0.3079</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3142</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8031</v>
+        <v>0.3079</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3625</v>
+        <v>0.3079</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4407</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2329</v>
+        <v>0.3079</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9415</v>
+        <v>0.3079</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2914</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4298</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5790999999999999</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1493</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4004</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4007</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5682</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8313</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.737</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3401</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUÑOZ</t>
+          <t>P. BAENA SÁNCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,28 +1111,28 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. BAENA SÁNCHEZ</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,28 +1189,28 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2999</v>
+        <v>0.1947</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2999</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2999</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2999</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2999</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2999</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1225,13 +1225,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>I. RUIPEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2001</v>
+        <v>-0.2434</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-1.1699</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2001</v>
+        <v>0.9265</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.5253</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.8364</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0.3111</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.5735</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.1232</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.6967</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.0988</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.3856</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2001</v>
+        <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.0978</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.0498</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9916</v>
+        <v>-2.631</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3452</v>
+        <v>-2.0225</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6463</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0159</v>
+        <v>-2.0022</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2891</v>
+        <v>-1.2793</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7268</v>
+        <v>-0.7229</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.894</v>
+        <v>-1.8509</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.296</v>
+        <v>-1.2674</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1218</v>
+        <v>-0.1513</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0069</v>
+        <v>-0.0118</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9162</v>
+        <v>-0.5178</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4512</v>
+        <v>-0.1717</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4651</v>
+        <v>-0.3461</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0461</v>
+        <v>-2.8983</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5872</v>
+        <v>-2.2311</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4589</v>
+        <v>-0.6672</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8404</v>
+        <v>0.8161</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0269</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8673</v>
+        <v>0.8248</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3709</v>
+        <v>-0.2236</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2672</v>
+        <v>0.4004</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.638</v>
+        <v>-0.624</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2113</v>
+        <v>1.0397</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2941</v>
+        <v>-0.4091</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5053</v>
+        <v>1.4488</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8267</v>
+        <v>-0.6297</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4755</v>
+        <v>-0.3396</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3512</v>
+        <v>-0.2901</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.0594</v>
+        <v>-2.1111</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3192</v>
+        <v>-2.3905</v>
       </c>
     </row>
     <row r="14">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.1871</v>
+        <v>-3.2977</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.6859</v>
+        <v>-4.95</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4988</v>
+        <v>1.6523</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.2703</v>
+        <v>-1.3381</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7816</v>
+        <v>-0.8339</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4887</v>
+        <v>-0.5042</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.532</v>
+        <v>-2.4738</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.216</v>
+        <v>-1.1853</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.316</v>
+        <v>-1.2885</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2618</v>
+        <v>1.1357</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4345</v>
+        <v>0.3514</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8273</v>
+        <v>0.7843</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3166</v>
+        <v>-1.3754</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1533</v>
+        <v>-0.5288</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1634</v>
+        <v>-0.8466</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.3112</v>
+        <v>-5.1666</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.7131</v>
+        <v>-3.9573</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5981</v>
+        <v>-1.2093</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0321</v>
+        <v>-0.0439</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5278</v>
+        <v>-0.6113</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5599</v>
+        <v>0.5674</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4942</v>
+        <v>-0.4309</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1799</v>
+        <v>0.1847</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6742</v>
+        <v>-0.6156</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5263</v>
+        <v>0.387</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7078</v>
+        <v>-0.796</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2341</v>
+        <v>1.183</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0568</v>
+        <v>0.2667</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2177</v>
+        <v>0.3683</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2745</v>
+        <v>-0.1015</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7269999999999994</v>
+        <v>-0.4520999999999997</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.5849</v>
+        <v>-10.1544</v>
       </c>
       <c r="F16" t="n">
-        <v>11.858</v>
+        <v>9.702400000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>4.711600000000001</v>
+        <v>4.6843</v>
       </c>
       <c r="H16" t="n">
-        <v>4.746</v>
+        <v>4.6515</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.03440000000000021</v>
+        <v>0.03280000000000027</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.8382</v>
+        <v>-1.6593</v>
       </c>
       <c r="K16" t="n">
-        <v>5.469199999999999</v>
+        <v>6.1508</v>
       </c>
       <c r="L16" t="n">
-        <v>-8.307399999999999</v>
+        <v>-7.8102</v>
       </c>
       <c r="M16" t="n">
-        <v>7.550000000000001</v>
+        <v>6.343499999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7231000000000001</v>
+        <v>-1.4993</v>
       </c>
       <c r="O16" t="n">
-        <v>8.273199999999999</v>
+        <v>7.8428</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0006</v>
+        <v>-1.9475</v>
       </c>
       <c r="Q16" t="n">
-        <v>-17.0049</v>
+        <v>-16.5527</v>
       </c>
       <c r="R16" t="n">
-        <v>15.0043</v>
+        <v>14.6051</v>
       </c>
       <c r="S16" t="n">
-        <v>-4.7793</v>
+        <v>-4.3886</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4992</v>
+        <v>-0.9460000000000002</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.2805</v>
+        <v>-3.4427</v>
       </c>
       <c r="V16" t="n">
-        <v>1.341499999999999</v>
+        <v>1.1995</v>
       </c>
       <c r="W16" t="n">
-        <v>8.757400000000001</v>
+        <v>9.003200000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.415900000000001</v>
+        <v>-7.8037</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BEDIA FERRER</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.1557</v>
+        <v>4.2879</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8392</v>
+        <v>1.9928</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3165</v>
+        <v>2.295</v>
       </c>
       <c r="G17" t="n">
-        <v>0.331</v>
+        <v>0.3273</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0949</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2362</v>
+        <v>1.1282</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0527</v>
+        <v>-0.1019</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1327</v>
+        <v>-0.0536</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08</v>
+        <v>-0.0483</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3838</v>
+        <v>0.4292</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2276</v>
+        <v>-0.7473</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1562</v>
+        <v>1.1764</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6005</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6005</v>
+        <v>1.9474</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5643</v>
+        <v>1.3422</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3723</v>
+        <v>0.8131</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1919</v>
+        <v>0.529</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3401</v>
+        <v>2.6184</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5196</v>
+        <v>3.229</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8597</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>J. BEDIA FERRER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.7427</v>
+        <v>3.6885</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2239</v>
+        <v>2.2607</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5189</v>
+        <v>1.4277</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2298</v>
+        <v>0.3421</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8969</v>
+        <v>0.1478</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1267</v>
+        <v>0.1943</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3815</v>
+        <v>0.0709</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2673</v>
+        <v>-0.0101</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1143</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.2712</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6296</v>
+        <v>0.158</v>
       </c>
       <c r="O18" t="n">
-        <v>1.241</v>
+        <v>0.1132</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.5579</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0006</v>
+        <v>1.5579</v>
       </c>
       <c r="S18" t="n">
-        <v>2.0142</v>
+        <v>2.1195</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5074</v>
+        <v>1.6308</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5068</v>
+        <v>0.4887</v>
       </c>
       <c r="V18" t="n">
-        <v>2.4987</v>
+        <v>-0.3311</v>
       </c>
       <c r="W18" t="n">
-        <v>3.0986</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5999</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. CAMPILLOS ALONSO</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0169</v>
+        <v>1.7983</v>
       </c>
       <c r="E19" t="n">
-        <v>0.706</v>
+        <v>-1.0452</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3109</v>
+        <v>2.8436</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3504</v>
+        <v>-0.0014</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9085</v>
+        <v>0.7877</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5580000000000001</v>
+        <v>-0.789</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0219</v>
+        <v>-1.3003</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02</v>
+        <v>1.4626</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0019</v>
+        <v>-2.7629</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3723</v>
+        <v>1.2989</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9285</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5561</v>
+        <v>1.9738</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0003</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0003</v>
+        <v>2.5316</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8327</v>
+        <v>0.605</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5157</v>
+        <v>0.0914</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.317</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1998</v>
+        <v>0.6105</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1998</v>
+        <v>2.1111</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. BLASCO NAVARRO</t>
+          <t>C. CAMPILLOS ALONSO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2489</v>
+        <v>1.6332</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2226</v>
+        <v>1.3694</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4715</v>
+        <v>0.2638</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1067</v>
+        <v>-0.4023</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5603</v>
+        <v>-0.9453</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4537</v>
+        <v>0.5429</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.256</v>
+        <v>0.045</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.296</v>
+        <v>0.0205</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04</v>
+        <v>0.0244</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1494</v>
+        <v>-0.4473</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2643</v>
+        <v>-0.9658</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4137</v>
+        <v>0.5185</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2003</v>
+        <v>0.9737</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1555</v>
+        <v>-0.1592</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0337</v>
+        <v>0.1034</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1217</v>
+        <v>-0.2626</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2073</v>
+        <v>1.0981</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9514</v>
+        <v>-1.0563</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7441</v>
+        <v>2.1544</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0518</v>
+        <v>0.9048</v>
       </c>
       <c r="H21" t="n">
-        <v>0.798</v>
+        <v>-0.4958</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8498</v>
+        <v>1.4005</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5411</v>
+        <v>0.4572</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3632</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.9044</v>
+        <v>-0.0483</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4893</v>
+        <v>0.4475</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5653</v>
+        <v>-1.0013</v>
       </c>
       <c r="O21" t="n">
-        <v>2.0546</v>
+        <v>1.4488</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6002</v>
+        <v>0.9737</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0006</v>
+        <v>-1.1684</v>
       </c>
       <c r="R21" t="n">
-        <v>2.6007</v>
+        <v>2.1421</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3555</v>
+        <v>0.1096</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4691</v>
+        <v>-0.3451</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1136</v>
+        <v>0.4548</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5999</v>
+        <v>-0.89</v>
       </c>
       <c r="W21" t="n">
-        <v>2.0594</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4596</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>L. BLASCO NAVARRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3017</v>
+        <v>-0.6542</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2576</v>
+        <v>-1.8785</v>
       </c>
       <c r="F22" t="n">
-        <v>1.956</v>
+        <v>1.2243</v>
       </c>
       <c r="G22" t="n">
-        <v>0.945</v>
+        <v>-1.1124</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.446</v>
+        <v>-1.5451</v>
       </c>
       <c r="I22" t="n">
-        <v>1.391</v>
+        <v>0.4327</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3474</v>
+        <v>-1.2269</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4617</v>
+        <v>-1.2674</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1143</v>
+        <v>0.0405</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5976</v>
+        <v>0.1145</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9077</v>
+        <v>-0.2776</v>
       </c>
       <c r="O22" t="n">
-        <v>1.5053</v>
+        <v>0.3921</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0003</v>
+        <v>0.1947</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.2003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2006</v>
+        <v>1.1684</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3873</v>
+        <v>0.2635</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4047</v>
+        <v>0.3221</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0174</v>
+        <v>-0.0586</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8597</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4218</v>
+        <v>-0.8581</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0945</v>
+        <v>-0.1666</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3273</v>
+        <v>-0.6915</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4587</v>
+        <v>0.3975</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1843</v>
+        <v>-0.1955</v>
       </c>
       <c r="I23" t="n">
-        <v>0.643</v>
+        <v>0.593</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4817</v>
+        <v>0.525</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4017</v>
+        <v>0.4439</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.023</v>
+        <v>-0.1275</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5119</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2005</v>
+        <v>-0.5671</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1046</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3051</v>
+        <v>-0.485</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2801</v>
+        <v>-1.2726</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="24">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2497</v>
+        <v>-1.3998</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1984</v>
+        <v>-1.4353</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0513</v>
+        <v>0.0355</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0067</v>
+        <v>-1.0092</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8779</v>
+        <v>-0.8698</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3287</v>
+        <v>-0.3447</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4975</v>
+        <v>0.3036</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4202</v>
+        <v>0.1181</v>
       </c>
       <c r="U24" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.1855</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.5762</v>
+        <v>-1.4177</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0662</v>
+        <v>-3.1142</v>
       </c>
       <c r="F25" t="n">
-        <v>1.49</v>
+        <v>1.6965</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.9428</v>
+        <v>-1.9077</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3155</v>
+        <v>0.3176</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.2583</v>
+        <v>-2.2254</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.3703</v>
+        <v>-2.2762</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3017</v>
+        <v>0.3413</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.672</v>
+        <v>-2.6175</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4275</v>
+        <v>0.3685</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0138</v>
+        <v>-0.0236</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4137</v>
+        <v>0.3921</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3736</v>
+        <v>0.7695</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6957</v>
+        <v>0.1357</v>
       </c>
       <c r="U25" t="n">
-        <v>0.322</v>
+        <v>0.6338</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.6544</v>
+        <v>-2.6084</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.8223</v>
+        <v>-3.519</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1679</v>
+        <v>0.9106</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.347</v>
+        <v>-2.329</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.5803</v>
+        <v>-1.5656</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7667</v>
+        <v>-0.7634</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.9883</v>
+        <v>-2.8791</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.9943</v>
+        <v>-0.9261</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.994</v>
+        <v>-1.953</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6413</v>
+        <v>0.5501</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O26" t="n">
-        <v>1.2273</v>
+        <v>1.1896</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4326</v>
+        <v>0.4675</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1533</v>
+        <v>-0.0304</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5858</v>
+        <v>0.4979</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9416</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.0264</v>
+        <v>-3.4775</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.0141</v>
+        <v>-3.1101</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0123</v>
+        <v>-0.3674</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1292</v>
+        <v>0.1061</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4999</v>
+        <v>0.5132</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3706</v>
+        <v>-0.4071</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8671</v>
+        <v>1.0072</v>
       </c>
       <c r="K27" t="n">
-        <v>1.5432</v>
+        <v>1.6473</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.6761</v>
+        <v>-0.6401</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.7378</v>
+        <v>-0.9012</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.0433</v>
+        <v>-1.1342</v>
       </c>
       <c r="O27" t="n">
-        <v>0.3055</v>
+        <v>0.233</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="R27" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S27" t="n">
-        <v>1.265</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>1.0805</v>
+        <v>0.6858</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1845</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.2201</v>
+        <v>-2.2142</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.7605</v>
+        <v>-0.7137</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="28">
@@ -2593,67 +2593,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7267000000000006</v>
+        <v>2.0903</v>
       </c>
       <c r="E28" t="n">
-        <v>-11.858</v>
+        <v>-9.702300000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>12.5849</v>
+        <v>11.7925</v>
       </c>
       <c r="G28" t="n">
-        <v>-4.7117</v>
+        <v>-4.684200000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>-4.7459</v>
+        <v>-4.6517</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0344999999999997</v>
+        <v>-0.03279999999999983</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.5498</v>
+        <v>-6.3436</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7231999999999998</v>
+        <v>1.4994</v>
       </c>
       <c r="L28" t="n">
-        <v>-8.273199999999999</v>
+        <v>-7.843000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>2.8385</v>
+        <v>1.6592</v>
       </c>
       <c r="N28" t="n">
-        <v>-5.469200000000001</v>
+        <v>-6.1508</v>
       </c>
       <c r="O28" t="n">
-        <v>8.307700000000001</v>
+        <v>7.8099</v>
       </c>
       <c r="P28" t="n">
-        <v>2.000799999999999</v>
+        <v>1.9473</v>
       </c>
       <c r="Q28" t="n">
-        <v>-15.0042</v>
+        <v>-14.6053</v>
       </c>
       <c r="R28" t="n">
-        <v>17.0049</v>
+        <v>16.5527</v>
       </c>
       <c r="S28" t="n">
-        <v>4.7795</v>
+        <v>6.0268</v>
       </c>
       <c r="T28" t="n">
-        <v>3.280199999999999</v>
+        <v>3.4428</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4989</v>
+        <v>2.5841</v>
       </c>
       <c r="V28" t="n">
-        <v>-1.3416</v>
+        <v>-1.1995</v>
       </c>
       <c r="W28" t="n">
-        <v>7.415899999999999</v>
+        <v>7.803999999999999</v>
       </c>
       <c r="X28" t="n">
-        <v>-8.7576</v>
+        <v>-9.0031</v>
       </c>
     </row>
   </sheetData>
